--- a/data/pending_jobs.xlsx
+++ b/data/pending_jobs.xlsx
@@ -1,34 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Pending Jobs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="Pending Jobs" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>fetched_at</t>
+  </si>
+  <si>
+    <t>https://jobright.ai/jobs/info/6aa1f4af2f936e4a53daee0d</t>
+  </si>
+  <si>
+    <t>https://jobright.ai/jobs/info/6a8ef6c2d7c91d0cf446cbd7</t>
+  </si>
+  <si>
+    <t>https://jobright.ai/jobs/info/6aa1f0ecdbc0e60e37e144cf</t>
+  </si>
+  <si>
+    <t>Wed Sep 09 2026 20:40:04 GMT-0500 (Central Daylight Time)</t>
+  </si>
+  <si>
+    <t>https://jobright.ai/jobs/info/6940a7d5aa598a08c3f04c0f</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/m/d h:mm"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +74,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -199,6 +169,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +204,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +239,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,37 +370,95 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="42.142857142857146" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>fetched_at</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/data/pending_jobs.xlsx
+++ b/data/pending_jobs.xlsx
@@ -1,62 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Pending Jobs" state="visible" r:id="rId4"/>
+    <sheet name="Pending Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>url</t>
-  </si>
-  <si>
-    <t>fetched_at</t>
-  </si>
-  <si>
-    <t>https://jobright.ai/jobs/info/6aa1f4af2f936e4a53daee0d</t>
-  </si>
-  <si>
-    <t>https://jobright.ai/jobs/info/6a8ef6c2d7c91d0cf446cbd7</t>
-  </si>
-  <si>
-    <t>https://jobright.ai/jobs/info/6aa1f0ecdbc0e60e37e144cf</t>
-  </si>
-  <si>
-    <t>Wed Sep 09 2026 20:40:04 GMT-0500 (Central Daylight Time)</t>
-  </si>
-  <si>
-    <t>https://jobright.ai/jobs/info/6940a7d5aa598a08c3f04c0f</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy/m/d h:mm"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -75,22 +50,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -169,7 +203,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -204,7 +237,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -239,16 +271,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -370,95 +406,47 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42.142857142857146" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fetched_at</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa44025422289703bd65d49</t>
+        </is>
       </c>
-      <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
+      <c r="B2" s="1" t="n">
+        <v>46277.12659722222</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/pending_jobs.xlsx
+++ b/data/pending_jobs.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,7 +50,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -439,12 +438,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6aa44025422289703bd65d49</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>46277.12659722222</v>
-      </c>
+          <t>https://jobright.ai/jobs/info/6a7288f3cb96192a3684e7c6</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a7cbbdf83621355407ab897</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a467c7c971cd25b06f8ee69</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aaaee5ef6bd9d2d17c1a711</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aab8c54f6bd9d2d17c1cb87</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aaa9f57c85610f4a4840a9a</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a05c8bc7c753c287f6fb895</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aaac0a740807b73bd391b17</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a95c0cdcabc9f6703e19976</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa9f4a26d0edc2d91b0cc13</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pending_jobs.xlsx
+++ b/data/pending_jobs.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6a7288f3cb96192a3684e7c6</t>
+          <t>https://jobright.ai/jobs/info/6a921369a27a2d3c9848b462</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -446,7 +446,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6a7cbbdf83621355407ab897</t>
+          <t>https://jobright.ai/jobs/info/6ab2c74478c69ff506c407ab</t>
         </is>
       </c>
       <c r="B3" s="1" t="n"/>
@@ -454,7 +454,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6a467c7c971cd25b06f8ee69</t>
+          <t>https://jobright.ai/jobs/info/6ab3085f1508734c1530d794</t>
         </is>
       </c>
       <c r="B4" s="1" t="n"/>
@@ -462,58 +462,10 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6aaaee5ef6bd9d2d17c1a711</t>
+          <t>https://jobright.ai/jobs/info/6ab2b40c78c69ff506c400d8</t>
         </is>
       </c>
       <c r="B5" s="1" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6aab8c54f6bd9d2d17c1cb87</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6aaa9f57c85610f4a4840a9a</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6a05c8bc7c753c287f6fb895</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6aaac0a740807b73bd391b17</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6a95c0cdcabc9f6703e19976</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6aa9f4a26d0edc2d91b0cc13</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pending_jobs.xlsx
+++ b/data/pending_jobs.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6a921369a27a2d3c9848b462</t>
+          <t>https://jobright.ai/jobs/info/6aadbe686956574eac8b76dc</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -446,7 +446,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6ab2c74478c69ff506c407ab</t>
+          <t>https://jobright.ai/jobs/info/6a92670bc12c90443efc9de7</t>
         </is>
       </c>
       <c r="B3" s="1" t="n"/>
@@ -454,7 +454,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6ab3085f1508734c1530d794</t>
+          <t>https://jobright.ai/jobs/info/69d6baefe63cea7a8b66b98f</t>
         </is>
       </c>
       <c r="B4" s="1" t="n"/>
@@ -462,10 +462,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6ab2b40c78c69ff506c400d8</t>
+          <t>https://jobright.ai/jobs/info/6a71768ccb96192a36848fe5</t>
         </is>
       </c>
       <c r="B5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a9af73bd5ff1f3f1c39caae</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa1f8c7ef23570cae24718e</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab9f93381e327c4bf206b59</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a6a62a848355b3f12bf0a89</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pending_jobs.xlsx
+++ b/data/pending_jobs.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6aadbe686956574eac8b76dc</t>
+          <t>https://jobright.ai/jobs/info/6ad00e48c0dd9da253cf61b8</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -446,7 +446,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6a92670bc12c90443efc9de7</t>
+          <t>https://jobright.ai/jobs/info/6a9b40ad90a313642c6595f4</t>
         </is>
       </c>
       <c r="B3" s="1" t="n"/>
@@ -454,7 +454,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/69d6baefe63cea7a8b66b98f</t>
+          <t>https://jobright.ai/jobs/info/6aa9c9faeff87f571fc9b92a</t>
         </is>
       </c>
       <c r="B4" s="1" t="n"/>
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6a71768ccb96192a36848fe5</t>
+          <t>https://jobright.ai/jobs/info/6acf48d4e57eb78d5ec0b2d1</t>
         </is>
       </c>
       <c r="B5" s="1" t="n"/>
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6a9af73bd5ff1f3f1c39caae</t>
+          <t>https://jobright.ai/jobs/info/6a9691da69b865490a632b36</t>
         </is>
       </c>
       <c r="B6" s="1" t="n"/>
@@ -478,7 +478,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6aa1f8c7ef23570cae24718e</t>
+          <t>https://jobright.ai/jobs/info/6acfc23ffe7a9bd5a6b99c1f</t>
         </is>
       </c>
       <c r="B7" s="1" t="n"/>
@@ -486,7 +486,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6ab9f93381e327c4bf206b59</t>
+          <t>https://jobright.ai/jobs/info/6aaae4d84be87a72913a1fdc</t>
         </is>
       </c>
       <c r="B8" s="1" t="n"/>
@@ -494,10 +494,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6a6a62a848355b3f12bf0a89</t>
+          <t>https://jobright.ai/jobs/info/6acff9bfc9f40bec907ff317</t>
         </is>
       </c>
       <c r="B9" s="1" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/69ebb7e258811370cb13bfab</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a67b69d3b5e6b116a55032c</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6abea79c8ff3fb9b3bc74e80</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
